--- a/17 18 20/Excel/02.Data Management Data Cleaning/ConditionalFormatting.xlsx
+++ b/17 18 20/Excel/02.Data Management Data Cleaning/ConditionalFormatting.xlsx
@@ -15,6 +15,9 @@
     <sheet name="Conditional Formatting" sheetId="18" r:id="rId1"/>
     <sheet name="Conditional Formatting(Formula)" sheetId="19" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Conditional Formatting(Formula)'!$A$36:$J$46</definedName>
+  </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="111">
   <si>
     <t>age</t>
   </si>
@@ -312,31 +315,52 @@
     <t>Formula</t>
   </si>
   <si>
-    <t>=$F29&lt;50000</t>
-  </si>
-  <si>
-    <t>=F16&gt;50000</t>
-  </si>
-  <si>
-    <t>=A16</t>
-  </si>
-  <si>
     <t>Applied To</t>
   </si>
   <si>
     <t>=A44:G44</t>
   </si>
   <si>
-    <t>=AND(F44&lt;59000,E44&lt;24)</t>
-  </si>
-  <si>
     <t>Ex Formula</t>
   </si>
   <si>
-    <t>Range on which condition should be performed</t>
-  </si>
-  <si>
-    <t>Age is less than 25</t>
+    <t>=C3</t>
+  </si>
+  <si>
+    <t>=E3&gt;25</t>
+  </si>
+  <si>
+    <t>Ex 01</t>
+  </si>
+  <si>
+    <t>Ex 02</t>
+  </si>
+  <si>
+    <t>=E3&gt;66000</t>
+  </si>
+  <si>
+    <t>=$F29&lt;60000</t>
+  </si>
+  <si>
+    <t>salary less than 60000</t>
+  </si>
+  <si>
+    <t>Salary is greater than 590000</t>
+  </si>
+  <si>
+    <t>age is less than 24</t>
+  </si>
+  <si>
+    <t>logic 01</t>
+  </si>
+  <si>
+    <t>logic 02</t>
+  </si>
+  <si>
+    <t>and</t>
+  </si>
+  <si>
+    <t>=AND($F83&lt;59000,$E44&lt;83)</t>
   </si>
 </sst>
 </file>
@@ -348,7 +372,7 @@
     <numFmt numFmtId="164" formatCode="dd/mmm/yyyy"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -424,6 +448,12 @@
       <name val="Candara"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Candara"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -491,7 +521,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1" readingOrder="1"/>
@@ -567,6 +597,25 @@
     <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -575,7 +624,799 @@
     <cellStyle name="Neutral" xfId="3" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="44">
+  <dxfs count="160">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -586,6 +1427,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="8" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -593,6 +1441,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -682,6 +1544,63 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
@@ -775,6 +1694,48 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="5" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -853,34 +1814,6 @@
       <fill>
         <patternFill>
           <bgColor theme="7" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2264,16 +3197,16 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G22:G35">
-    <cfRule type="timePeriod" dxfId="43" priority="5" timePeriod="tomorrow">
+    <cfRule type="timePeriod" dxfId="40" priority="5" timePeriod="tomorrow">
       <formula>FLOOR(G22,1)=TODAY()+1</formula>
     </cfRule>
-    <cfRule type="timePeriod" dxfId="42" priority="6" timePeriod="yesterday">
+    <cfRule type="timePeriod" dxfId="39" priority="6" timePeriod="yesterday">
       <formula>FLOOR(G22,1)=TODAY()-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B22:B35">
-    <cfRule type="uniqueValues" dxfId="41" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="4"/>
+    <cfRule type="uniqueValues" dxfId="38" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F16">
     <cfRule type="dataBar" priority="2">
@@ -2323,7 +3256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:O75"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" style="3" bestFit="1" customWidth="1"/>
@@ -2331,18 +3264,30 @@
     <col min="3" max="3" width="10.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.109375" style="3" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.88671875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.77734375" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="3"/>
-    <col min="10" max="10" width="15.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.88671875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.44140625" style="3" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="14" width="10.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="3"/>
+    <col min="15" max="15" width="10" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="L1" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="M1" s="31"/>
+      <c r="O1" s="31" t="s">
+        <v>101</v>
+      </c>
+      <c r="P1" s="31"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>49</v>
       </c>
@@ -2367,17 +3312,20 @@
       <c r="H2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="L2" s="21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="M2" s="21" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="O2" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="P2" s="21" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" s="22">
         <v>101</v>
       </c>
@@ -2402,18 +3350,20 @@
       <c r="H3" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="3" t="b">
-        <f>E3&lt;25</f>
-        <v>1</v>
-      </c>
       <c r="L3" s="25" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M3" s="25" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+      <c r="O3" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="P3" s="25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="22">
         <v>102</v>
       </c>
@@ -2438,42 +3388,36 @@
       <c r="H4" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J4" s="3" t="b">
-        <f t="shared" ref="J4:J12" si="0">E4&lt;25</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="22">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="32">
         <v>103</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="32">
         <v>22</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="32">
         <v>75000</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="33">
         <v>44032</v>
       </c>
-      <c r="H5" s="26" t="s">
+      <c r="H5" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="J5" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="22">
         <v>104</v>
       </c>
@@ -2498,42 +3442,36 @@
       <c r="H6" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J6" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="22">
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="32">
         <v>105</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="32">
         <v>24</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="32">
         <v>72000</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="33">
         <v>44699</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="H7" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="J7" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="22">
         <v>106</v>
       </c>
@@ -2558,12 +3496,8 @@
       <c r="H8" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="J8" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="22">
         <v>107</v>
       </c>
@@ -2588,72 +3522,64 @@
       <c r="H9" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="22">
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="32">
         <v>108</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="32">
         <v>27</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="32">
         <v>67000</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="33">
         <v>44809</v>
       </c>
-      <c r="H10" s="27" t="s">
+      <c r="H10" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="22">
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="32">
         <v>109</v>
       </c>
       <c r="B11" s="22" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="32">
         <v>28</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="32">
         <v>80000</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="33">
         <v>43811</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="I11" s="35"/>
+      <c r="J11" s="35"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="22">
         <v>110</v>
       </c>
@@ -2677,15 +3603,6 @@
       </c>
       <c r="H12" s="24" t="s">
         <v>45</v>
-      </c>
-      <c r="J12" s="3" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L15" s="3" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
@@ -2713,6 +3630,9 @@
       <c r="H36" s="20" t="s">
         <v>48</v>
       </c>
+      <c r="J36" s="3" t="s">
+        <v>104</v>
+      </c>
       <c r="L36" s="21" t="s">
         <v>94</v>
       </c>
@@ -2721,1014 +3641,1124 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="22">
+      <c r="A37" s="32">
         <v>101</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="22">
+      <c r="E37" s="32">
         <v>20</v>
       </c>
-      <c r="F37" s="22">
+      <c r="F37" s="32">
         <v>50000</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="33">
         <v>44573</v>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H37" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="I37" s="3" t="b">
+      <c r="I37" s="35"/>
+      <c r="J37" s="35" t="b">
         <f>F37&lt;60000</f>
         <v>1</v>
       </c>
       <c r="L37" s="25" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="M37" s="25" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="22">
+      <c r="A38" s="32">
         <v>102</v>
       </c>
-      <c r="B38" s="22" t="s">
+      <c r="B38" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D38" s="32" t="s">
         <v>59</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="32">
         <v>21</v>
       </c>
-      <c r="F38" s="22">
+      <c r="F38" s="32">
         <v>60000</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="33">
         <v>44270</v>
       </c>
-      <c r="H38" s="24" t="s">
+      <c r="H38" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="I38" s="3" t="b">
-        <f t="shared" ref="I38:I46" si="1">F38&lt;60000</f>
+      <c r="J38" s="3" t="b">
+        <f t="shared" ref="J38:J46" si="0">F38&lt;60000</f>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="22">
+      <c r="A39" s="32">
         <v>103</v>
       </c>
-      <c r="B39" s="22" t="s">
+      <c r="B39" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D39" s="32" t="s">
         <v>62</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="32">
         <v>22</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="32">
         <v>75000</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="33">
         <v>44032</v>
       </c>
-      <c r="H39" s="24" t="s">
+      <c r="H39" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="I39" s="3" t="b">
+      <c r="J39" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="32">
+        <v>104</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E40" s="32">
+        <v>23</v>
+      </c>
+      <c r="F40" s="32">
+        <v>65000</v>
+      </c>
+      <c r="G40" s="33">
+        <v>44967</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="J40" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="32">
+        <v>105</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E41" s="32">
+        <v>24</v>
+      </c>
+      <c r="F41" s="32">
+        <v>72000</v>
+      </c>
+      <c r="G41" s="33">
+        <v>44699</v>
+      </c>
+      <c r="H41" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="J41" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="32">
+        <v>106</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C42" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="32">
+        <v>25</v>
+      </c>
+      <c r="F42" s="32">
+        <v>48000</v>
+      </c>
+      <c r="G42" s="33">
+        <v>44433</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="32">
+        <v>107</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="C43" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E43" s="32">
+        <v>26</v>
+      </c>
+      <c r="F43" s="32">
+        <v>61000</v>
+      </c>
+      <c r="G43" s="33">
+        <v>44165</v>
+      </c>
+      <c r="H43" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="J43" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="32">
+        <v>108</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="E44" s="32">
+        <v>27</v>
+      </c>
+      <c r="F44" s="32">
+        <v>67000</v>
+      </c>
+      <c r="G44" s="33">
+        <v>44809</v>
+      </c>
+      <c r="H44" s="37" t="s">
+        <v>47</v>
+      </c>
+      <c r="J44" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="32">
+        <v>109</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="32">
+        <v>28</v>
+      </c>
+      <c r="F45" s="32">
+        <v>80000</v>
+      </c>
+      <c r="G45" s="33">
+        <v>43811</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="J45" s="3" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A46" s="32">
+        <v>110</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E46" s="32">
+        <v>29</v>
+      </c>
+      <c r="F46" s="32">
+        <v>52000</v>
+      </c>
+      <c r="G46" s="33">
+        <v>45017</v>
+      </c>
+      <c r="H46" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35" t="b">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B66" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F66" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G66" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H66" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="O66" s="20" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="22">
+        <v>105</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C67" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E67" s="22">
+        <v>24</v>
+      </c>
+      <c r="F67" s="22">
+        <v>72000</v>
+      </c>
+      <c r="G67" s="28">
+        <v>44699</v>
+      </c>
+      <c r="H67" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L67" s="3" t="b">
+        <f>H67="HOLD"</f>
+        <v>0</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="22">
+        <v>108</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E68" s="22">
+        <v>27</v>
+      </c>
+      <c r="F68" s="22">
+        <v>67000</v>
+      </c>
+      <c r="G68" s="28">
+        <v>44809</v>
+      </c>
+      <c r="H68" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="L68" s="3" t="b">
+        <f>H67="Pending"</f>
+        <v>0</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="22">
+        <v>101</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E69" s="22">
+        <v>20</v>
+      </c>
+      <c r="F69" s="22">
+        <v>50000</v>
+      </c>
+      <c r="G69" s="28">
+        <v>44573</v>
+      </c>
+      <c r="H69" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="L69" s="3" t="b">
+        <f>H67="Confirmed"</f>
+        <v>1</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="22">
+        <v>103</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E70" s="22">
+        <v>22</v>
+      </c>
+      <c r="F70" s="22">
+        <v>75000</v>
+      </c>
+      <c r="G70" s="28">
+        <v>44032</v>
+      </c>
+      <c r="H70" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="22">
+        <v>106</v>
+      </c>
+      <c r="B71" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" s="22">
+        <v>25</v>
+      </c>
+      <c r="F71" s="22">
+        <v>48000</v>
+      </c>
+      <c r="G71" s="28">
+        <v>44433</v>
+      </c>
+      <c r="H71" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A72" s="22">
+        <v>109</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72" s="22">
+        <v>28</v>
+      </c>
+      <c r="F72" s="22">
+        <v>80000</v>
+      </c>
+      <c r="G72" s="28">
+        <v>43811</v>
+      </c>
+      <c r="H72" s="26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A73" s="22">
+        <v>102</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E73" s="22">
+        <v>21</v>
+      </c>
+      <c r="F73" s="22">
+        <v>60000</v>
+      </c>
+      <c r="G73" s="28">
+        <v>44270</v>
+      </c>
+      <c r="H73" s="24" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="22">
+        <v>104</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C74" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E74" s="22">
+        <v>23</v>
+      </c>
+      <c r="F74" s="22">
+        <v>65000</v>
+      </c>
+      <c r="G74" s="28">
+        <v>44967</v>
+      </c>
+      <c r="H74" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A75" s="22">
+        <v>107</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="22">
+        <v>26</v>
+      </c>
+      <c r="F75" s="22">
+        <v>61000</v>
+      </c>
+      <c r="G75" s="28">
+        <v>44165</v>
+      </c>
+      <c r="H75" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="22">
+        <v>110</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C76" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E76" s="22">
+        <v>29</v>
+      </c>
+      <c r="F76" s="22">
+        <v>52000</v>
+      </c>
+      <c r="G76" s="28">
+        <v>45017</v>
+      </c>
+      <c r="H76" s="24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="J80" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="J81" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A82" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C82" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E82" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F82" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="G82" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="H82" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K82" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="M82" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="P82" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q82" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A83" s="22">
+        <v>101</v>
+      </c>
+      <c r="B83" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="C83" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E83" s="22">
+        <v>20</v>
+      </c>
+      <c r="F83" s="30">
+        <v>60000</v>
+      </c>
+      <c r="G83" s="28">
+        <v>44573</v>
+      </c>
+      <c r="H83" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J83" s="3" t="b">
+        <f>F83&gt;59000</f>
+        <v>1</v>
+      </c>
+      <c r="K83" s="3" t="b">
+        <f>E83&lt;24</f>
+        <v>1</v>
+      </c>
+      <c r="L83" s="3" t="b">
+        <f>AND($F83&gt;59000,$E83&lt;24)</f>
+        <v>1</v>
+      </c>
+      <c r="P83" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q83" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A84" s="22">
+        <v>102</v>
+      </c>
+      <c r="B84" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E84" s="22">
+        <v>21</v>
+      </c>
+      <c r="F84" s="30">
+        <v>60000</v>
+      </c>
+      <c r="G84" s="28">
+        <v>44270</v>
+      </c>
+      <c r="H84" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J84" s="3" t="b">
+        <f t="shared" ref="J84:J92" si="1">F84&gt;59000</f>
+        <v>1</v>
+      </c>
+      <c r="K84" s="3" t="b">
+        <f t="shared" ref="K84:K92" si="2">E84&lt;24</f>
+        <v>1</v>
+      </c>
+      <c r="L84" s="3" t="b">
+        <f t="shared" ref="L84:L92" si="3">AND(F84&gt;59000,E84&lt;24)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A85" s="22">
+        <v>103</v>
+      </c>
+      <c r="B85" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="C85" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E85" s="22">
+        <v>22</v>
+      </c>
+      <c r="F85" s="30">
+        <v>75000</v>
+      </c>
+      <c r="G85" s="28">
+        <v>44032</v>
+      </c>
+      <c r="H85" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J85" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K85" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L85" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="P85" s="3" t="b">
+        <f>AND(F83&lt;59000,E83&lt;24)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A86" s="22">
+        <v>104</v>
+      </c>
+      <c r="B86" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="C86" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E86" s="22">
+        <v>23</v>
+      </c>
+      <c r="F86" s="30">
+        <v>65000</v>
+      </c>
+      <c r="G86" s="28">
+        <v>44967</v>
+      </c>
+      <c r="H86" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J86" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K86" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L86" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A87" s="22">
+        <v>105</v>
+      </c>
+      <c r="B87" s="22" t="s">
+        <v>66</v>
+      </c>
+      <c r="C87" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E87" s="22">
+        <v>24</v>
+      </c>
+      <c r="F87" s="30">
+        <v>72000</v>
+      </c>
+      <c r="G87" s="28">
+        <v>44699</v>
+      </c>
+      <c r="H87" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J87" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K87" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L87" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A88" s="22">
+        <v>106</v>
+      </c>
+      <c r="B88" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E88" s="22">
+        <v>25</v>
+      </c>
+      <c r="F88" s="30">
+        <v>48000</v>
+      </c>
+      <c r="G88" s="28">
+        <v>44433</v>
+      </c>
+      <c r="H88" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J88" s="3" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="22">
-        <v>104</v>
-      </c>
-      <c r="B40" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C40" s="22" t="s">
+      <c r="K88" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L88" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A89" s="22">
+        <v>107</v>
+      </c>
+      <c r="B89" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="E89" s="22">
+        <v>26</v>
+      </c>
+      <c r="F89" s="30">
+        <v>61000</v>
+      </c>
+      <c r="G89" s="28">
+        <v>44165</v>
+      </c>
+      <c r="H89" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="J89" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K89" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L89" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A90" s="22">
+        <v>108</v>
+      </c>
+      <c r="B90" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="C90" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="D40" s="22" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" s="22">
+      <c r="D90" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E90" s="22">
         <v>23</v>
       </c>
-      <c r="F40" s="22">
-        <v>65000</v>
-      </c>
-      <c r="G40" s="23">
-        <v>44967</v>
-      </c>
-      <c r="H40" s="24" t="s">
+      <c r="F90" s="30">
+        <v>61000</v>
+      </c>
+      <c r="G90" s="28">
+        <v>44809</v>
+      </c>
+      <c r="H90" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="J90" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K90" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="L90" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A91" s="22">
+        <v>109</v>
+      </c>
+      <c r="B91" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="C91" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E91" s="22">
+        <v>28</v>
+      </c>
+      <c r="F91" s="30">
+        <v>80000</v>
+      </c>
+      <c r="G91" s="28">
+        <v>43811</v>
+      </c>
+      <c r="H91" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="J91" s="3" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K91" s="3" t="b">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="L91" s="3" t="b">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A92" s="22">
+        <v>110</v>
+      </c>
+      <c r="B92" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C92" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E92" s="22">
+        <v>29</v>
+      </c>
+      <c r="F92" s="30">
+        <v>52000</v>
+      </c>
+      <c r="G92" s="28">
+        <v>45017</v>
+      </c>
+      <c r="H92" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="I40" s="3" t="b">
+      <c r="J92" s="3" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="22">
-        <v>105</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="E41" s="22">
-        <v>24</v>
-      </c>
-      <c r="F41" s="22">
-        <v>72000</v>
-      </c>
-      <c r="G41" s="23">
-        <v>44699</v>
-      </c>
-      <c r="H41" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I41" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="22">
-        <v>106</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>67</v>
-      </c>
-      <c r="E42" s="22">
-        <v>25</v>
-      </c>
-      <c r="F42" s="22">
-        <v>48000</v>
-      </c>
-      <c r="G42" s="23">
-        <v>44433</v>
-      </c>
-      <c r="H42" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="22">
-        <v>107</v>
-      </c>
-      <c r="B43" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D43" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="E43" s="22">
-        <v>26</v>
-      </c>
-      <c r="F43" s="22">
-        <v>61000</v>
-      </c>
-      <c r="G43" s="23">
-        <v>44165</v>
-      </c>
-      <c r="H43" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I43" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="22">
-        <v>108</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C44" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E44" s="22">
-        <v>27</v>
-      </c>
-      <c r="F44" s="22">
-        <v>67000</v>
-      </c>
-      <c r="G44" s="23">
-        <v>44809</v>
-      </c>
-      <c r="H44" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="I44" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="22">
-        <v>109</v>
-      </c>
-      <c r="B45" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="E45" s="22">
-        <v>28</v>
-      </c>
-      <c r="F45" s="22">
-        <v>80000</v>
-      </c>
-      <c r="G45" s="23">
-        <v>43811</v>
-      </c>
-      <c r="H45" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I45" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="22">
-        <v>110</v>
-      </c>
-      <c r="B46" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C46" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="E46" s="22">
-        <v>29</v>
-      </c>
-      <c r="F46" s="22">
-        <v>52000</v>
-      </c>
-      <c r="G46" s="23">
-        <v>45017</v>
-      </c>
-      <c r="H46" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I46" s="3" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B50" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D50" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="F50" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="G50" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H50" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="O50" s="20" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="22">
-        <v>101</v>
-      </c>
-      <c r="B51" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" s="22">
-        <v>20</v>
-      </c>
-      <c r="F51" s="22">
-        <v>50000</v>
-      </c>
-      <c r="G51" s="28">
-        <v>44573</v>
-      </c>
-      <c r="H51" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="L51" s="3" t="b">
-        <f>H51="HOLD"</f>
-        <v>1</v>
-      </c>
-      <c r="O51" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A52" s="22">
-        <v>102</v>
-      </c>
-      <c r="B52" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C52" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E52" s="22">
-        <v>21</v>
-      </c>
-      <c r="F52" s="22">
-        <v>60000</v>
-      </c>
-      <c r="G52" s="28">
-        <v>44270</v>
-      </c>
-      <c r="H52" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="L52" s="3" t="b">
-        <f>H51="Pending"</f>
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="22">
-        <v>103</v>
-      </c>
-      <c r="B53" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53" s="22">
-        <v>22</v>
-      </c>
-      <c r="F53" s="22">
-        <v>75000</v>
-      </c>
-      <c r="G53" s="28">
-        <v>44032</v>
-      </c>
-      <c r="H53" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="L53" s="3" t="b">
-        <f>H51="Confirmed"</f>
-        <v>0</v>
-      </c>
-      <c r="O53" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A54" s="22">
-        <v>104</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C54" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E54" s="22">
-        <v>23</v>
-      </c>
-      <c r="F54" s="22">
-        <v>65000</v>
-      </c>
-      <c r="G54" s="28">
-        <v>44967</v>
-      </c>
-      <c r="H54" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="22">
-        <v>105</v>
-      </c>
-      <c r="B55" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C55" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E55" s="22">
-        <v>24</v>
-      </c>
-      <c r="F55" s="22">
-        <v>72000</v>
-      </c>
-      <c r="G55" s="28">
-        <v>44699</v>
-      </c>
-      <c r="H55" s="27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="22">
-        <v>106</v>
-      </c>
-      <c r="B56" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C56" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E56" s="22">
-        <v>25</v>
-      </c>
-      <c r="F56" s="22">
-        <v>48000</v>
-      </c>
-      <c r="G56" s="28">
-        <v>44433</v>
-      </c>
-      <c r="H56" s="26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="22">
-        <v>107</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C57" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E57" s="22">
-        <v>26</v>
-      </c>
-      <c r="F57" s="22">
-        <v>61000</v>
-      </c>
-      <c r="G57" s="28">
-        <v>44165</v>
-      </c>
-      <c r="H57" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="22">
-        <v>108</v>
-      </c>
-      <c r="B58" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C58" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E58" s="22">
-        <v>27</v>
-      </c>
-      <c r="F58" s="22">
-        <v>67000</v>
-      </c>
-      <c r="G58" s="28">
-        <v>44809</v>
-      </c>
-      <c r="H58" s="27" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" s="22">
-        <v>109</v>
-      </c>
-      <c r="B59" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C59" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E59" s="22">
-        <v>28</v>
-      </c>
-      <c r="F59" s="22">
-        <v>80000</v>
-      </c>
-      <c r="G59" s="28">
-        <v>43811</v>
-      </c>
-      <c r="H59" s="26" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" s="22">
-        <v>110</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C60" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E60" s="22">
-        <v>29</v>
-      </c>
-      <c r="F60" s="22">
-        <v>52000</v>
-      </c>
-      <c r="G60" s="28">
-        <v>45017</v>
-      </c>
-      <c r="H60" s="24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A65" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B65" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="C65" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>52</v>
-      </c>
-      <c r="E65" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="F65" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="H65" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="L65" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="M65" s="20" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A66" s="22">
-        <v>101</v>
-      </c>
-      <c r="B66" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="C66" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E66" s="22">
-        <v>20</v>
-      </c>
-      <c r="F66" s="30">
-        <v>60000</v>
-      </c>
-      <c r="G66" s="28">
-        <v>44573</v>
-      </c>
-      <c r="H66" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="I66" s="3" t="b">
-        <f>AND(F66&gt;59000,E66&lt;24)</f>
-        <v>1</v>
-      </c>
-      <c r="L66" s="29" t="s">
-        <v>100</v>
-      </c>
-      <c r="M66" s="29" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A67" s="22">
-        <v>102</v>
-      </c>
-      <c r="B67" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="C67" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E67" s="22">
-        <v>21</v>
-      </c>
-      <c r="F67" s="30">
-        <v>60000</v>
-      </c>
-      <c r="G67" s="28">
-        <v>44270</v>
-      </c>
-      <c r="H67" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I67" s="3" t="b">
-        <f t="shared" ref="I67:I75" si="2">AND(F67&gt;59000,E67&lt;24)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A68" s="22">
-        <v>103</v>
-      </c>
-      <c r="B68" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="C68" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E68" s="22">
-        <v>22</v>
-      </c>
-      <c r="F68" s="30">
-        <v>75000</v>
-      </c>
-      <c r="G68" s="28">
-        <v>44032</v>
-      </c>
-      <c r="H68" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I68" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="L68" s="3" t="b">
-        <f>AND(F66&lt;59000,E66&lt;24)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A69" s="22">
-        <v>104</v>
-      </c>
-      <c r="B69" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="C69" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E69" s="22">
-        <v>23</v>
-      </c>
-      <c r="F69" s="30">
-        <v>65000</v>
-      </c>
-      <c r="G69" s="28">
-        <v>44967</v>
-      </c>
-      <c r="H69" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I69" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A70" s="22">
-        <v>105</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C70" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E70" s="22">
-        <v>24</v>
-      </c>
-      <c r="F70" s="30">
-        <v>72000</v>
-      </c>
-      <c r="G70" s="28">
-        <v>44699</v>
-      </c>
-      <c r="H70" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="I70" s="3" t="b">
+      <c r="K92" s="3" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A71" s="22">
-        <v>106</v>
-      </c>
-      <c r="B71" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C71" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71" s="22">
-        <v>25</v>
-      </c>
-      <c r="F71" s="30">
-        <v>48000</v>
-      </c>
-      <c r="G71" s="28">
-        <v>44433</v>
-      </c>
-      <c r="H71" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I71" s="3" t="b">
-        <f t="shared" si="2"/>
+      <c r="L92" s="3" t="b">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A72" s="22">
-        <v>107</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>68</v>
-      </c>
-      <c r="C72" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E72" s="22">
-        <v>26</v>
-      </c>
-      <c r="F72" s="30">
-        <v>61000</v>
-      </c>
-      <c r="G72" s="28">
-        <v>44165</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I72" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A73" s="22">
-        <v>108</v>
-      </c>
-      <c r="B73" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="C73" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E73" s="22">
-        <v>23</v>
-      </c>
-      <c r="F73" s="30">
-        <v>61000</v>
-      </c>
-      <c r="G73" s="28">
-        <v>44809</v>
-      </c>
-      <c r="H73" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="I73" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A74" s="22">
-        <v>109</v>
-      </c>
-      <c r="B74" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="C74" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E74" s="22">
-        <v>28</v>
-      </c>
-      <c r="F74" s="30">
-        <v>80000</v>
-      </c>
-      <c r="G74" s="28">
-        <v>43811</v>
-      </c>
-      <c r="H74" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="I74" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A75" s="22">
-        <v>110</v>
-      </c>
-      <c r="B75" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="C75" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E75" s="22">
-        <v>29</v>
-      </c>
-      <c r="F75" s="30">
-        <v>52000</v>
-      </c>
-      <c r="G75" s="28">
-        <v>45017</v>
-      </c>
-      <c r="H75" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="I75" s="3" t="b">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="B51">
-    <cfRule type="expression" dxfId="39" priority="22">
-      <formula>H51="Confirmed"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="38" priority="23">
-      <formula>H51="Pending"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="24">
-      <formula>H51="HOLD"</formula>
+  <autoFilter ref="A36:J46"/>
+  <sortState ref="A67:H76">
+    <sortCondition ref="H67:H76"/>
+  </sortState>
+  <mergeCells count="2">
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="O1:P1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B3">
+    <cfRule type="expression" dxfId="28" priority="13">
+      <formula>$F3&gt;66000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B52:B60">
-    <cfRule type="expression" dxfId="36" priority="19">
-      <formula>H52="Confirmed"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="20">
-      <formula>H52="Pending"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="21">
-      <formula>H52="HOLD"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B66">
-    <cfRule type="expression" dxfId="33" priority="10">
-      <formula>AND($F66&gt;59000,$E66&lt;24)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B67:B75">
-    <cfRule type="expression" dxfId="32" priority="8">
-      <formula>AND($F67&gt;59000,$E67&lt;24)</formula>
+  <conditionalFormatting sqref="B4:B12">
+    <cfRule type="expression" dxfId="27" priority="12">
+      <formula>$F4&gt;66000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A37:H37">
-    <cfRule type="expression" dxfId="29" priority="5">
+    <cfRule type="expression" dxfId="26" priority="10">
       <formula>$F37&lt;60000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A38:H46">
-    <cfRule type="expression" dxfId="28" priority="4">
+    <cfRule type="expression" dxfId="25" priority="9">
       <formula>$F38&lt;60000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$E3&lt;25</formula>
+  <conditionalFormatting sqref="B83">
+    <cfRule type="expression" dxfId="24" priority="8">
+      <formula>AND($F83&gt;59000,$E83&lt;24)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C4:C12">
+  <conditionalFormatting sqref="B84:B92">
+    <cfRule type="expression" dxfId="23" priority="7">
+      <formula>AND($F84&gt;59000,$E84&lt;24)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B67">
+    <cfRule type="expression" dxfId="6" priority="6">
+      <formula>$H67="HOLD"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="5">
+      <formula>$H67="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$H67="Confirmed"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B68:B76">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$E4&lt;25</formula>
+      <formula>$H68="Confirmed"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$H68="Pending"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>$H68="HOLD"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
